--- a/MGMP543/Week3IRR.xlsx
+++ b/MGMP543/Week3IRR.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10303"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gk/Dropbox/rice/teaching/Core Finance Evening MBA 2024-25 Spring (MGMP 543)/slides/Week3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE4A76B-96AA-104A-9F2E-915CFC9CC202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D244F36-1ABC-7143-B706-28D406D6D4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20440" yWindow="-1340" windowWidth="20440" windowHeight="17700" xr2:uid="{13800E5C-3516-C549-8CE1-EECD19873D99}"/>
+    <workbookView xWindow="-25360" yWindow="-1340" windowWidth="25360" windowHeight="17700" xr2:uid="{13800E5C-3516-C549-8CE1-EECD19873D99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="goalseekrate">Sheet1!$F$1</definedName>
     <definedName name="rate">Sheet1!$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>rate</t>
   </si>
@@ -57,6 +58,15 @@
   </si>
   <si>
     <t>rates</t>
+  </si>
+  <si>
+    <t>goalseekrate</t>
+  </si>
+  <si>
+    <t>&lt;- put some guess of a discount rate in here</t>
+  </si>
+  <si>
+    <t>data -&gt; What-If Analysis -&gt; Goal Seek -&gt; Set Cell: F2 -&gt; To Value: B9 -&gt; By Changing: F1.</t>
   </si>
 </sst>
 </file>
@@ -6991,16 +7001,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>736600</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7023,6 +7033,50 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{283DB4E9-8E69-324E-0EA2-6696F19F13E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6743700" y="469900"/>
+          <a:ext cx="4330700" cy="2184400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7345,29 +7399,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF73493-A938-9E4E-964B-6D5B5A315C2E}">
-  <dimension ref="A1:C1013"/>
+  <dimension ref="A1:G1013"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
         <v>0.11494</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1">
+        <v>0.05</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F2" s="4">
+        <f>NPV(goalseekrate,$B$4:$B$7)+$B$3</f>
+        <v>2045950.50416236</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>0</v>
       </c>
@@ -7379,7 +7452,7 @@
         <v>-1500000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -7391,7 +7464,7 @@
         <v>896909.2507220119</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -7403,7 +7476,7 @@
         <v>804446.20403072075</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -7415,7 +7488,7 @@
         <v>721515.24210336048</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -7427,12 +7500,12 @@
         <v>647133.69517943612</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
@@ -7440,32 +7513,35 @@
         <v>1570000</v>
       </c>
       <c r="C9" s="1">
-        <f>SUM(C3:C7)</f>
+        <f>SUM($C$3:$C$7)</f>
         <v>1570004.3920355293</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="4">
-        <f>NPV(11.5%,B$4:B$7)+B$3</f>
+        <f>NPV(11.5%,$B$4:$B$7)+$B$3</f>
         <v>1569613.7993824896</v>
       </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C10" s="4">
+        <f>NPV(11.5%,$B$4:$B$7)+$B$3</f>
+        <v>1569613.7993824896</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <f>IRR(B$3:B$7)</f>
+        <f>IRR($B$3:$B$7)</f>
         <v>0.55166020094065993</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -7473,26 +7549,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>1E-3</v>
       </c>
       <c r="B14" s="4">
-        <f>NPV($A14,B$4:B$7)+B$3</f>
+        <f>NPV($A14,$B$4:$B$7)+$B$3</f>
         <v>2490019.9650559174</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <f>A14+0.1%</f>
         <v>2E-3</v>
       </c>
       <c r="B15" s="4">
-        <f t="shared" ref="B15:B78" si="0">NPV($A15,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B15:B78" si="0">NPV($A15,$B$4:$B$7)+$B$3</f>
         <v>2480079.7208933197</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <f t="shared" ref="A16:A79" si="1">A15+0.1%</f>
         <v>3.0000000000000001E-3</v>
@@ -8128,7 +8204,7 @@
         <v>6.6000000000000045E-2</v>
       </c>
       <c r="B79" s="4">
-        <f t="shared" ref="B79:B142" si="2">NPV($A79,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B79:B142" si="2">NPV($A79,$B$4:$B$7)+$B$3</f>
         <v>1918024.1205922277</v>
       </c>
     </row>
@@ -8768,7 +8844,7 @@
         <v>0.13000000000000009</v>
       </c>
       <c r="B143" s="4">
-        <f t="shared" ref="B143:B206" si="4">NPV($A143,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B143:B206" si="4">NPV($A143,$B$4:$B$7)+$B$3</f>
         <v>1474471.3255432569</v>
       </c>
     </row>
@@ -9408,7 +9484,7 @@
         <v>0.19400000000000014</v>
       </c>
       <c r="B207" s="4">
-        <f t="shared" ref="B207:B270" si="6">NPV($A207,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B207:B270" si="6">NPV($A207,$B$4:$B$7)+$B$3</f>
         <v>1118453.9809959414</v>
       </c>
     </row>
@@ -10048,7 +10124,7 @@
         <v>0.25800000000000017</v>
       </c>
       <c r="B271" s="4">
-        <f t="shared" ref="B271:B334" si="8">NPV($A271,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B271:B334" si="8">NPV($A271,$B$4:$B$7)+$B$3</f>
         <v>828372.52525495552</v>
       </c>
     </row>
@@ -10688,7 +10764,7 @@
         <v>0.32200000000000023</v>
       </c>
       <c r="B335" s="4">
-        <f t="shared" ref="B335:B398" si="10">NPV($A335,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B335:B398" si="10">NPV($A335,$B$4:$B$7)+$B$3</f>
         <v>588830.40099427849</v>
       </c>
     </row>
@@ -11328,7 +11404,7 @@
         <v>0.38600000000000029</v>
       </c>
       <c r="B399" s="4">
-        <f t="shared" ref="B399:B462" si="12">NPV($A399,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B399:B462" si="12">NPV($A399,$B$4:$B$7)+$B$3</f>
         <v>388636.94282902242</v>
       </c>
     </row>
@@ -11968,7 +12044,7 @@
         <v>0.45000000000000034</v>
       </c>
       <c r="B463" s="4">
-        <f t="shared" ref="B463:B526" si="14">NPV($A463,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B463:B526" si="14">NPV($A463,$B$4:$B$7)+$B$3</f>
         <v>219514.59179590479</v>
       </c>
     </row>
@@ -12608,7 +12684,7 @@
         <v>0.51400000000000035</v>
       </c>
       <c r="B527" s="4">
-        <f t="shared" ref="B527:B590" si="16">NPV($A527,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B527:B590" si="16">NPV($A527,$B$4:$B$7)+$B$3</f>
         <v>75242.627192099812</v>
       </c>
     </row>
@@ -13248,7 +13324,7 @@
         <v>0.5780000000000004</v>
       </c>
       <c r="B591" s="4">
-        <f t="shared" ref="B591:B654" si="18">NPV($A591,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B591:B654" si="18">NPV($A591,$B$4:$B$7)+$B$3</f>
         <v>-48921.86791229574</v>
       </c>
     </row>
@@ -13888,7 +13964,7 @@
         <v>0.64200000000000046</v>
       </c>
       <c r="B655" s="4">
-        <f t="shared" ref="B655:B718" si="20">NPV($A655,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B655:B718" si="20">NPV($A655,$B$4:$B$7)+$B$3</f>
         <v>-156643.02409004234</v>
       </c>
     </row>
@@ -14528,7 +14604,7 @@
         <v>0.70600000000000052</v>
       </c>
       <c r="B719" s="4">
-        <f t="shared" ref="B719:B782" si="22">NPV($A719,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B719:B782" si="22">NPV($A719,$B$4:$B$7)+$B$3</f>
         <v>-250785.92921192572</v>
       </c>
     </row>
@@ -15168,7 +15244,7 @@
         <v>0.77000000000000057</v>
       </c>
       <c r="B783" s="4">
-        <f t="shared" ref="B783:B846" si="24">NPV($A783,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B783:B846" si="24">NPV($A783,$B$4:$B$7)+$B$3</f>
         <v>-333615.87305485155</v>
       </c>
     </row>
@@ -15808,7 +15884,7 @@
         <v>0.83400000000000063</v>
       </c>
       <c r="B847" s="4">
-        <f t="shared" ref="B847:B910" si="26">NPV($A847,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B847:B910" si="26">NPV($A847,$B$4:$B$7)+$B$3</f>
         <v>-406942.33397362777</v>
       </c>
     </row>
@@ -16448,7 +16524,7 @@
         <v>0.89800000000000069</v>
       </c>
       <c r="B911" s="4">
-        <f t="shared" ref="B911:B974" si="28">NPV($A911,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B911:B974" si="28">NPV($A911,$B$4:$B$7)+$B$3</f>
         <v>-472224.43745324016</v>
       </c>
     </row>
@@ -17088,7 +17164,7 @@
         <v>0.96200000000000074</v>
       </c>
       <c r="B975" s="4">
-        <f t="shared" ref="B975:B1013" si="30">NPV($A975,B$4:B$7)+B$3</f>
+        <f t="shared" ref="B975:B1013" si="30">NPV($A975,$B$4:$B$7)+$B$3</f>
         <v>-530649.16086009261</v>
       </c>
     </row>
